--- a/ledger_multi_account.xlsx
+++ b/ledger_multi_account.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="129">
   <si>
     <t>전표번호</t>
   </si>
@@ -190,6 +190,9 @@
     <t>JV1-0050</t>
   </si>
   <si>
+    <t>JV1-0051</t>
+  </si>
+  <si>
     <t>JV2-0001</t>
   </si>
   <si>
@@ -205,36 +208,6 @@
     <t>JV2-0005</t>
   </si>
   <si>
-    <t>JV2-0006</t>
-  </si>
-  <si>
-    <t>JV2-0007</t>
-  </si>
-  <si>
-    <t>JV2-0008</t>
-  </si>
-  <si>
-    <t>JV2-0009</t>
-  </si>
-  <si>
-    <t>JV2-0010</t>
-  </si>
-  <si>
-    <t>JV2-0011</t>
-  </si>
-  <si>
-    <t>JV2-0012</t>
-  </si>
-  <si>
-    <t>JV2-0013</t>
-  </si>
-  <si>
-    <t>JV2-0014</t>
-  </si>
-  <si>
-    <t>JV1-0051</t>
-  </si>
-  <si>
     <t>2026-08-11</t>
   </si>
   <si>
@@ -385,6 +358,9 @@
     <t>지급수수료</t>
   </si>
   <si>
+    <t>일일카드매출정산</t>
+  </si>
+  <si>
     <t>사무용품</t>
   </si>
   <si>
@@ -403,15 +379,15 @@
     <t>거래처 미팅 다과</t>
   </si>
   <si>
-    <t>일일카드매출정산</t>
-  </si>
-  <si>
     <t>법인카드사</t>
   </si>
   <si>
     <t>여비교통비</t>
   </si>
   <si>
+    <t>매출</t>
+  </si>
+  <si>
     <t>소모품비</t>
   </si>
   <si>
@@ -419,9 +395,6 @@
   </si>
   <si>
     <t>접대비</t>
-  </si>
-  <si>
-    <t>매출</t>
   </si>
   <si>
     <t>주거래 보통예금</t>
@@ -793,13 +766,13 @@
         <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="C2" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="D2" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -808,10 +781,10 @@
         <v>1310000</v>
       </c>
       <c r="G2" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H2" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -819,13 +792,13 @@
         <v>9</v>
       </c>
       <c r="B3" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="D3" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -834,10 +807,10 @@
         <v>1720000</v>
       </c>
       <c r="G3" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H3" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -845,13 +818,13 @@
         <v>10</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="D4" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -860,10 +833,10 @@
         <v>420000</v>
       </c>
       <c r="G4" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H4" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -871,13 +844,13 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="D5" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -886,10 +859,10 @@
         <v>1950000</v>
       </c>
       <c r="G5" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H5" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -897,13 +870,13 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="D6" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -912,10 +885,10 @@
         <v>1440000</v>
       </c>
       <c r="G6" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H6" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -923,13 +896,13 @@
         <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="D7" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -938,10 +911,10 @@
         <v>1040000</v>
       </c>
       <c r="G7" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H7" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -949,13 +922,13 @@
         <v>14</v>
       </c>
       <c r="B8" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="D8" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -964,10 +937,10 @@
         <v>910000</v>
       </c>
       <c r="G8" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H8" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -975,13 +948,13 @@
         <v>15</v>
       </c>
       <c r="B9" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="D9" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -990,10 +963,10 @@
         <v>380000</v>
       </c>
       <c r="G9" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H9" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1001,13 +974,13 @@
         <v>16</v>
       </c>
       <c r="B10" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="D10" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1016,10 +989,10 @@
         <v>1560000</v>
       </c>
       <c r="G10" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H10" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1027,13 +1000,13 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="D11" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -1042,10 +1015,10 @@
         <v>1650000</v>
       </c>
       <c r="G11" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H11" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -1053,13 +1026,13 @@
         <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="C12" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="D12" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -1068,10 +1041,10 @@
         <v>900000</v>
       </c>
       <c r="G12" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H12" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -1079,13 +1052,13 @@
         <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="D13" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1094,10 +1067,10 @@
         <v>210000</v>
       </c>
       <c r="G13" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H13" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1105,13 +1078,13 @@
         <v>20</v>
       </c>
       <c r="B14" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="D14" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1120,10 +1093,10 @@
         <v>150000</v>
       </c>
       <c r="G14" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H14" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15" spans="1:8">
@@ -1131,13 +1104,13 @@
         <v>21</v>
       </c>
       <c r="B15" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="C15" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="D15" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1146,10 +1119,10 @@
         <v>1660000</v>
       </c>
       <c r="G15" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H15" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1157,13 +1130,13 @@
         <v>22</v>
       </c>
       <c r="B16" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="C16" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="D16" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1172,10 +1145,10 @@
         <v>350000</v>
       </c>
       <c r="G16" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H16" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1183,13 +1156,13 @@
         <v>23</v>
       </c>
       <c r="B17" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="C17" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="D17" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1198,10 +1171,10 @@
         <v>720000</v>
       </c>
       <c r="G17" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H17" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1209,13 +1182,13 @@
         <v>24</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="C18" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="D18" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -1224,10 +1197,10 @@
         <v>1940000</v>
       </c>
       <c r="G18" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H18" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1235,13 +1208,13 @@
         <v>25</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="C19" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="D19" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1250,10 +1223,10 @@
         <v>1360000</v>
       </c>
       <c r="G19" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H19" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1261,13 +1234,13 @@
         <v>26</v>
       </c>
       <c r="B20" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="C20" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="D20" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1276,10 +1249,10 @@
         <v>410000</v>
       </c>
       <c r="G20" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H20" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1287,13 +1260,13 @@
         <v>27</v>
       </c>
       <c r="B21" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="C21" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="D21" t="s">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -1302,10 +1275,10 @@
         <v>940000</v>
       </c>
       <c r="G21" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H21" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1313,13 +1286,13 @@
         <v>28</v>
       </c>
       <c r="B22" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="C22" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="D22" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -1328,10 +1301,10 @@
         <v>1100000</v>
       </c>
       <c r="G22" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H22" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1339,13 +1312,13 @@
         <v>29</v>
       </c>
       <c r="B23" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="C23" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="D23" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -1354,10 +1327,10 @@
         <v>1370000</v>
       </c>
       <c r="G23" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H23" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="24" spans="1:8">
@@ -1365,13 +1338,13 @@
         <v>30</v>
       </c>
       <c r="B24" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C24" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="D24" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -1380,10 +1353,10 @@
         <v>750000</v>
       </c>
       <c r="G24" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H24" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1391,13 +1364,13 @@
         <v>31</v>
       </c>
       <c r="B25" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="C25" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="D25" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -1406,10 +1379,10 @@
         <v>830000</v>
       </c>
       <c r="G25" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H25" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1417,13 +1390,13 @@
         <v>32</v>
       </c>
       <c r="B26" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="C26" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="D26" t="s">
-        <v>109</v>
+        <v>100</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -1432,10 +1405,10 @@
         <v>750000</v>
       </c>
       <c r="G26" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H26" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1443,13 +1416,13 @@
         <v>33</v>
       </c>
       <c r="B27" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="C27" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="D27" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -1458,10 +1431,10 @@
         <v>1590000</v>
       </c>
       <c r="G27" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H27" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1469,13 +1442,13 @@
         <v>34</v>
       </c>
       <c r="B28" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C28" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="D28" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -1484,10 +1457,10 @@
         <v>280000</v>
       </c>
       <c r="G28" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H28" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1495,13 +1468,13 @@
         <v>35</v>
       </c>
       <c r="B29" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="C29" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="D29" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -1510,10 +1483,10 @@
         <v>680000</v>
       </c>
       <c r="G29" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H29" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1521,13 +1494,13 @@
         <v>36</v>
       </c>
       <c r="B30" t="s">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="C30" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="D30" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -1536,10 +1509,10 @@
         <v>1140000</v>
       </c>
       <c r="G30" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H30" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1547,13 +1520,13 @@
         <v>37</v>
       </c>
       <c r="B31" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C31" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="D31" t="s">
-        <v>115</v>
+        <v>106</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -1562,10 +1535,10 @@
         <v>890000</v>
       </c>
       <c r="G31" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H31" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1573,13 +1546,13 @@
         <v>38</v>
       </c>
       <c r="B32" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C32" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="D32" t="s">
-        <v>116</v>
+        <v>107</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -1588,10 +1561,10 @@
         <v>1670000</v>
       </c>
       <c r="G32" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H32" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="33" spans="1:8">
@@ -1599,13 +1572,13 @@
         <v>39</v>
       </c>
       <c r="B33" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="C33" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="D33" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -1614,10 +1587,10 @@
         <v>220000</v>
       </c>
       <c r="G33" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H33" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="34" spans="1:8">
@@ -1625,13 +1598,13 @@
         <v>40</v>
       </c>
       <c r="B34" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="C34" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="D34" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -1640,10 +1613,10 @@
         <v>1540000</v>
       </c>
       <c r="G34" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H34" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="35" spans="1:8">
@@ -1651,13 +1624,13 @@
         <v>41</v>
       </c>
       <c r="B35" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="C35" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="D35" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -1666,10 +1639,10 @@
         <v>1610000</v>
       </c>
       <c r="G35" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H35" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="36" spans="1:8">
@@ -1677,13 +1650,13 @@
         <v>42</v>
       </c>
       <c r="B36" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="C36" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="D36" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -1692,10 +1665,10 @@
         <v>790000</v>
       </c>
       <c r="G36" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H36" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="37" spans="1:8">
@@ -1703,13 +1676,13 @@
         <v>43</v>
       </c>
       <c r="B37" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="C37" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="D37" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -1718,10 +1691,10 @@
         <v>500000</v>
       </c>
       <c r="G37" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H37" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="38" spans="1:8">
@@ -1729,13 +1702,13 @@
         <v>44</v>
       </c>
       <c r="B38" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="C38" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="D38" t="s">
-        <v>105</v>
+        <v>96</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -1744,10 +1717,10 @@
         <v>1280000</v>
       </c>
       <c r="G38" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H38" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="39" spans="1:8">
@@ -1755,13 +1728,13 @@
         <v>45</v>
       </c>
       <c r="B39" t="s">
+        <v>89</v>
+      </c>
+      <c r="C39" t="s">
         <v>98</v>
       </c>
-      <c r="C39" t="s">
-        <v>107</v>
-      </c>
       <c r="D39" t="s">
-        <v>107</v>
+        <v>98</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -1770,10 +1743,10 @@
         <v>420000</v>
       </c>
       <c r="G39" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H39" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="40" spans="1:8">
@@ -1781,13 +1754,13 @@
         <v>46</v>
       </c>
       <c r="B40" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="C40" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="D40" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -1796,10 +1769,10 @@
         <v>1590000</v>
       </c>
       <c r="G40" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H40" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="41" spans="1:8">
@@ -1807,13 +1780,13 @@
         <v>47</v>
       </c>
       <c r="B41" t="s">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="C41" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="D41" t="s">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -1822,10 +1795,10 @@
         <v>1560000</v>
       </c>
       <c r="G41" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H41" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="42" spans="1:8">
@@ -1833,13 +1806,13 @@
         <v>48</v>
       </c>
       <c r="B42" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="C42" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="D42" t="s">
-        <v>106</v>
+        <v>97</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -1848,10 +1821,10 @@
         <v>1410000</v>
       </c>
       <c r="G42" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H42" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="43" spans="1:8">
@@ -1859,13 +1832,13 @@
         <v>49</v>
       </c>
       <c r="B43" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="C43" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="D43" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -1874,10 +1847,10 @@
         <v>1560000</v>
       </c>
       <c r="G43" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H43" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -1885,13 +1858,13 @@
         <v>50</v>
       </c>
       <c r="B44" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C44" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="D44" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -1900,10 +1873,10 @@
         <v>1020000</v>
       </c>
       <c r="G44" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H44" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="45" spans="1:8">
@@ -1911,13 +1884,13 @@
         <v>51</v>
       </c>
       <c r="B45" t="s">
+        <v>92</v>
+      </c>
+      <c r="C45" t="s">
         <v>101</v>
       </c>
-      <c r="C45" t="s">
-        <v>110</v>
-      </c>
       <c r="D45" t="s">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -1926,10 +1899,10 @@
         <v>100000</v>
       </c>
       <c r="G45" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H45" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -1937,13 +1910,13 @@
         <v>52</v>
       </c>
       <c r="B46" t="s">
+        <v>93</v>
+      </c>
+      <c r="C46" t="s">
         <v>102</v>
       </c>
-      <c r="C46" t="s">
-        <v>111</v>
-      </c>
       <c r="D46" t="s">
-        <v>111</v>
+        <v>102</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -1952,10 +1925,10 @@
         <v>250000</v>
       </c>
       <c r="G46" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H46" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="47" spans="1:8">
@@ -1963,13 +1936,13 @@
         <v>53</v>
       </c>
       <c r="B47" t="s">
-        <v>102</v>
+        <v>93</v>
       </c>
       <c r="C47" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="D47" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -1978,10 +1951,10 @@
         <v>130000</v>
       </c>
       <c r="G47" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H47" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="48" spans="1:8">
@@ -1989,13 +1962,13 @@
         <v>54</v>
       </c>
       <c r="B48" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C48" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="D48" t="s">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="E48">
         <v>80000</v>
@@ -2004,10 +1977,10 @@
         <v>0</v>
       </c>
       <c r="G48" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H48" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="49" spans="1:8">
@@ -2015,13 +1988,13 @@
         <v>55</v>
       </c>
       <c r="B49" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="C49" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="D49" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -2030,10 +2003,10 @@
         <v>1015</v>
       </c>
       <c r="G49" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="H49" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="50" spans="1:8">
@@ -2041,13 +2014,13 @@
         <v>56</v>
       </c>
       <c r="B50" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C50" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="D50" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -2056,10 +2029,10 @@
         <v>55000</v>
       </c>
       <c r="G50" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H50" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -2067,10 +2040,10 @@
         <v>57</v>
       </c>
       <c r="B51" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="C51" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -2079,10 +2052,10 @@
         <v>500</v>
       </c>
       <c r="G51" t="s">
-        <v>122</v>
+        <v>113</v>
       </c>
       <c r="H51" t="s">
-        <v>136</v>
+        <v>127</v>
       </c>
     </row>
     <row r="52" spans="1:8">
@@ -2090,25 +2063,22 @@
         <v>58</v>
       </c>
       <c r="B52" t="s">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="C52" t="s">
+        <v>114</v>
+      </c>
+      <c r="E52">
+        <v>300000</v>
+      </c>
+      <c r="F52">
+        <v>0</v>
+      </c>
+      <c r="G52" t="s">
         <v>123</v>
       </c>
-      <c r="D52" t="s">
-        <v>130</v>
-      </c>
-      <c r="E52">
-        <v>0</v>
-      </c>
-      <c r="F52">
-        <v>500000</v>
-      </c>
-      <c r="G52" t="s">
-        <v>132</v>
-      </c>
       <c r="H52" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
     </row>
     <row r="53" spans="1:8">
@@ -2116,360 +2086,363 @@
         <v>59</v>
       </c>
       <c r="B53" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="C53" t="s">
+        <v>115</v>
+      </c>
+      <c r="D53" t="s">
+        <v>121</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+      <c r="F53">
+        <v>500000</v>
+      </c>
+      <c r="G53" t="s">
         <v>124</v>
       </c>
-      <c r="D53" t="s">
-        <v>130</v>
-      </c>
-      <c r="E53">
-        <v>0</v>
-      </c>
-      <c r="F53">
-        <v>170000</v>
-      </c>
-      <c r="G53" t="s">
-        <v>131</v>
-      </c>
       <c r="H53" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B54" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="C54" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="D54" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="E54">
         <v>0</v>
       </c>
       <c r="F54">
-        <v>80000</v>
+        <v>170000</v>
       </c>
       <c r="G54" t="s">
         <v>122</v>
       </c>
       <c r="H54" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B55" t="s">
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="C55" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D55" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="E55">
         <v>0</v>
       </c>
       <c r="F55">
-        <v>50000</v>
+        <v>80000</v>
       </c>
       <c r="G55" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="H55" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B56" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="C56" t="s">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="D56" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="E56">
         <v>0</v>
       </c>
       <c r="F56">
-        <v>320000</v>
+        <v>50000</v>
       </c>
       <c r="G56" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="H56" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B57" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="C57" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="D57" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="E57">
         <v>0</v>
       </c>
       <c r="F57">
-        <v>210000</v>
+        <v>320000</v>
       </c>
       <c r="G57" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="H57" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B58" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="C58" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D58" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="E58">
         <v>0</v>
       </c>
       <c r="F58">
-        <v>230000</v>
+        <v>210000</v>
       </c>
       <c r="G58" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="H58" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="B59" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="C59" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="D59" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="E59">
         <v>0</v>
       </c>
       <c r="F59">
-        <v>200000</v>
+        <v>230000</v>
       </c>
       <c r="G59" t="s">
         <v>122</v>
       </c>
       <c r="H59" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="B60" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="C60" t="s">
-        <v>126</v>
+        <v>117</v>
       </c>
       <c r="D60" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="E60">
         <v>0</v>
       </c>
       <c r="F60">
-        <v>370000</v>
+        <v>200000</v>
       </c>
       <c r="G60" t="s">
-        <v>133</v>
+        <v>113</v>
       </c>
       <c r="H60" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B61" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C61" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D61" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="E61">
         <v>0</v>
       </c>
       <c r="F61">
-        <v>350000</v>
+        <v>370000</v>
       </c>
       <c r="G61" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="H61" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B62" t="s">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="C62" t="s">
+        <v>115</v>
+      </c>
+      <c r="D62" t="s">
+        <v>121</v>
+      </c>
+      <c r="E62">
+        <v>0</v>
+      </c>
+      <c r="F62">
+        <v>350000</v>
+      </c>
+      <c r="G62" t="s">
+        <v>124</v>
+      </c>
+      <c r="H62" t="s">
         <v>128</v>
-      </c>
-      <c r="D62" t="s">
-        <v>130</v>
-      </c>
-      <c r="E62">
-        <v>0</v>
-      </c>
-      <c r="F62">
-        <v>330000</v>
-      </c>
-      <c r="G62" t="s">
-        <v>134</v>
-      </c>
-      <c r="H62" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="C63" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D63" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="E63">
         <v>0</v>
       </c>
       <c r="F63">
-        <v>590000</v>
+        <v>330000</v>
       </c>
       <c r="G63" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="H63" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C64" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="D64" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="E64">
         <v>0</v>
       </c>
       <c r="F64">
-        <v>300000</v>
+        <v>590000</v>
       </c>
       <c r="G64" t="s">
         <v>122</v>
       </c>
       <c r="H64" t="s">
-        <v>137</v>
+        <v>128</v>
       </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>101</v>
+        <v>92</v>
       </c>
       <c r="C65" t="s">
+        <v>117</v>
+      </c>
+      <c r="D65" t="s">
+        <v>121</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
+      <c r="F65">
+        <v>300000</v>
+      </c>
+      <c r="G65" t="s">
+        <v>113</v>
+      </c>
+      <c r="H65" t="s">
         <v>128</v>
-      </c>
-      <c r="D65" t="s">
-        <v>130</v>
-      </c>
-      <c r="E65">
-        <v>0</v>
-      </c>
-      <c r="F65">
-        <v>160000</v>
-      </c>
-      <c r="G65" t="s">
-        <v>134</v>
-      </c>
-      <c r="H65" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="B66" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="C66" t="s">
-        <v>129</v>
+        <v>120</v>
+      </c>
+      <c r="D66" t="s">
+        <v>121</v>
       </c>
       <c r="E66">
-        <v>300000</v>
+        <v>0</v>
       </c>
       <c r="F66">
-        <v>0</v>
+        <v>160000</v>
       </c>
       <c r="G66" t="s">
-        <v>135</v>
+        <v>126</v>
       </c>
       <c r="H66" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
